--- a/stick-world/config/excel/运输数据.xlsx
+++ b/stick-world/config/excel/运输数据.xlsx
@@ -820,7 +820,7 @@
         </is>
       </c>
       <c r="D4" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="E4" t="n">
         <v>10</v>
@@ -849,16 +849,16 @@
         </is>
       </c>
       <c r="D5" t="n">
-        <v>80</v>
+        <v>20</v>
       </c>
       <c r="E5" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="F5" t="n">
         <v>15</v>
       </c>
       <c r="G5" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="H5" t="inlineStr">
         <is>
@@ -883,16 +883,16 @@
         </is>
       </c>
       <c r="D6" t="n">
-        <v>200</v>
+        <v>40</v>
       </c>
       <c r="E6" t="n">
-        <v>50</v>
+        <v>20</v>
       </c>
       <c r="F6" t="n">
         <v>30</v>
       </c>
       <c r="G6" t="n">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="H6" t="inlineStr">
         <is>
@@ -917,7 +917,7 @@
         </is>
       </c>
       <c r="D7" t="n">
-        <v>500</v>
+        <v>80</v>
       </c>
       <c r="E7" t="n">
         <v>0</v>
@@ -926,7 +926,7 @@
         <v>60</v>
       </c>
       <c r="G7" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="H7" t="inlineStr">
         <is>
@@ -1094,10 +1094,8 @@
           <t>木材</t>
         </is>
       </c>
-      <c r="I4" t="inlineStr">
-        <is>
-          <t>10</t>
-        </is>
+      <c r="I4" t="n">
+        <v>10</v>
       </c>
       <c r="J4" t="inlineStr">
         <is>
@@ -1140,10 +1138,8 @@
           <t>木材,金属</t>
         </is>
       </c>
-      <c r="I5" t="inlineStr">
-        <is>
-          <t>30</t>
-        </is>
+      <c r="I5" t="n">
+        <v>20</v>
       </c>
       <c r="J5" t="inlineStr">
         <is>
@@ -1186,10 +1182,8 @@
           <t>木材</t>
         </is>
       </c>
-      <c r="I6" t="inlineStr">
-        <is>
-          <t>15</t>
-        </is>
+      <c r="I6" t="n">
+        <v>10</v>
       </c>
       <c r="J6" t="inlineStr">
         <is>
@@ -1232,10 +1226,8 @@
           <t>木材</t>
         </is>
       </c>
-      <c r="I7" t="inlineStr">
-        <is>
-          <t>40</t>
-        </is>
+      <c r="I7" t="n">
+        <v>20</v>
       </c>
       <c r="J7" t="inlineStr">
         <is>
@@ -1278,10 +1270,8 @@
           <t>木材,金属</t>
         </is>
       </c>
-      <c r="I8" t="inlineStr">
-        <is>
-          <t>80</t>
-        </is>
+      <c r="I8" t="n">
+        <v>40</v>
       </c>
       <c r="J8" t="inlineStr">
         <is>
@@ -1324,10 +1314,8 @@
           <t>木材,金属</t>
         </is>
       </c>
-      <c r="I9" t="inlineStr">
-        <is>
-          <t>60</t>
-        </is>
+      <c r="I9" t="n">
+        <v>30</v>
       </c>
       <c r="J9" t="inlineStr">
         <is>
@@ -1370,10 +1358,8 @@
           <t>木材,金属</t>
         </is>
       </c>
-      <c r="I10" t="inlineStr">
-        <is>
-          <t>100</t>
-        </is>
+      <c r="I10" t="n">
+        <v>50</v>
       </c>
       <c r="J10" t="inlineStr">
         <is>
@@ -1416,10 +1402,8 @@
           <t>木材,金属</t>
         </is>
       </c>
-      <c r="I11" t="inlineStr">
-        <is>
-          <t>50</t>
-        </is>
+      <c r="I11" t="n">
+        <v>30</v>
       </c>
       <c r="J11" t="inlineStr">
         <is>

--- a/stick-world/config/excel/运输数据.xlsx
+++ b/stick-world/config/excel/运输数据.xlsx
@@ -820,10 +820,10 @@
         </is>
       </c>
       <c r="D4" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="E4" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="F4" t="n">
         <v>5</v>
@@ -849,10 +849,10 @@
         </is>
       </c>
       <c r="D5" t="n">
-        <v>20</v>
+        <v>18</v>
       </c>
       <c r="E5" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="F5" t="n">
         <v>15</v>
@@ -883,10 +883,10 @@
         </is>
       </c>
       <c r="D6" t="n">
-        <v>40</v>
+        <v>38</v>
       </c>
       <c r="E6" t="n">
-        <v>20</v>
+        <v>18</v>
       </c>
       <c r="F6" t="n">
         <v>30</v>
@@ -917,7 +917,7 @@
         </is>
       </c>
       <c r="D7" t="n">
-        <v>80</v>
+        <v>75</v>
       </c>
       <c r="E7" t="n">
         <v>0</v>
@@ -926,7 +926,7 @@
         <v>60</v>
       </c>
       <c r="G7" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="H7" t="inlineStr">
         <is>
@@ -1095,7 +1095,7 @@
         </is>
       </c>
       <c r="I4" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="J4" t="inlineStr">
         <is>
@@ -1139,7 +1139,7 @@
         </is>
       </c>
       <c r="I5" t="n">
-        <v>20</v>
+        <v>18</v>
       </c>
       <c r="J5" t="inlineStr">
         <is>
@@ -1183,7 +1183,7 @@
         </is>
       </c>
       <c r="I6" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="J6" t="inlineStr">
         <is>
@@ -1227,7 +1227,7 @@
         </is>
       </c>
       <c r="I7" t="n">
-        <v>20</v>
+        <v>18</v>
       </c>
       <c r="J7" t="inlineStr">
         <is>
@@ -1271,7 +1271,7 @@
         </is>
       </c>
       <c r="I8" t="n">
-        <v>40</v>
+        <v>38</v>
       </c>
       <c r="J8" t="inlineStr">
         <is>
@@ -1315,7 +1315,7 @@
         </is>
       </c>
       <c r="I9" t="n">
-        <v>30</v>
+        <v>28</v>
       </c>
       <c r="J9" t="inlineStr">
         <is>
@@ -1359,7 +1359,7 @@
         </is>
       </c>
       <c r="I10" t="n">
-        <v>50</v>
+        <v>45</v>
       </c>
       <c r="J10" t="inlineStr">
         <is>
@@ -1403,7 +1403,7 @@
         </is>
       </c>
       <c r="I11" t="n">
-        <v>30</v>
+        <v>28</v>
       </c>
       <c r="J11" t="inlineStr">
         <is>
